--- a/artfynd/A 40934-2020 artfynd.xlsx
+++ b/artfynd/A 40934-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40934-2020 artfynd.xlsx
+++ b/artfynd/A 40934-2020 artfynd.xlsx
@@ -2082,7 +2082,7 @@
         <v>89691778</v>
       </c>
       <c r="B13" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419961.993773242</v>
+        <v>419962</v>
       </c>
       <c r="R13" t="n">
-        <v>6586490.724474113</v>
+        <v>6586491</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2161,19 +2161,9 @@
           <t>2020-12-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-12-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">

--- a/artfynd/A 40934-2020 artfynd.xlsx
+++ b/artfynd/A 40934-2020 artfynd.xlsx
@@ -4154,7 +4154,7 @@
         <v>117596846</v>
       </c>
       <c r="B30" t="n">
-        <v>97003</v>
+        <v>97005</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2020 artfynd.xlsx
+++ b/artfynd/A 40934-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4251,6 +4251,108 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123370883</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Strax W Mjölnartorpets lekplats, Strax W Mjölnartorpets lekplats, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>419913</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6586411</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Johan Bohlin</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Johan Bohlin</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40934-2020 artfynd.xlsx
+++ b/artfynd/A 40934-2020 artfynd.xlsx
@@ -4256,7 +4256,7 @@
         <v>123370883</v>
       </c>
       <c r="B31" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2020 artfynd.xlsx
+++ b/artfynd/A 40934-2020 artfynd.xlsx
@@ -4256,7 +4256,7 @@
         <v>123370883</v>
       </c>
       <c r="B31" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2020 artfynd.xlsx
+++ b/artfynd/A 40934-2020 artfynd.xlsx
@@ -4256,7 +4256,7 @@
         <v>123370883</v>
       </c>
       <c r="B31" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2020 artfynd.xlsx
+++ b/artfynd/A 40934-2020 artfynd.xlsx
@@ -4256,7 +4256,7 @@
         <v>123370883</v>
       </c>
       <c r="B31" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2020 artfynd.xlsx
+++ b/artfynd/A 40934-2020 artfynd.xlsx
@@ -4256,7 +4256,7 @@
         <v>123370883</v>
       </c>
       <c r="B31" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2020 artfynd.xlsx
+++ b/artfynd/A 40934-2020 artfynd.xlsx
@@ -4256,7 +4256,7 @@
         <v>123370883</v>
       </c>
       <c r="B31" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2020 artfynd.xlsx
+++ b/artfynd/A 40934-2020 artfynd.xlsx
@@ -4256,7 +4256,7 @@
         <v>123370883</v>
       </c>
       <c r="B31" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
